--- a/restaurant_crawler/restaurant_data_台北_熱炒_20250910_192957_with_emails.xlsx
+++ b/restaurant_crawler/restaurant_data_台北_熱炒_20250910_192957_with_emails.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\slow3\OneDrive\桌面\GitHubProjects\BYOB\restaurant_crawler\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D0F4B9E-E93A-4AC1-85C0-00FB904C9867}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{905694E2-4437-4290-B1AC-E4E6BD55765A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="294">
   <si>
     <t>name</t>
   </si>
@@ -713,18 +713,6 @@
   </si>
   <si>
     <t>ChIJc0bak8yrQjQRa6SGK9i5gks</t>
-  </si>
-  <si>
-    <t>鑫鱻熱炒店</t>
-  </si>
-  <si>
-    <t>114台灣台北市內湖區瑞光路288號</t>
-  </si>
-  <si>
-    <t>02 2658 6881</t>
-  </si>
-  <si>
-    <t>ChIJ65qNOnusQjQRencjU0S-G2s</t>
   </si>
   <si>
     <t>半斤九兩食品有限公司-台北 台菜海鮮熱炒 喜宴 謝師宴 同學會聚餐 尾牙 活海鮮 辦桌 推薦中餐廳 生猛海鮮餐廳推薦 年菜圍爐 外帶年菜 年夜飯 海鮮料理 私房料理 台灣料理</t>
@@ -1475,35 +1463,6 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>231</v>
-      </c>
-      <c r="B7" t="s">
-        <v>232</v>
-      </c>
-      <c r="C7" t="s">
-        <v>233</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E7">
-        <v>3.7</v>
-      </c>
-      <c r="F7">
-        <v>1609</v>
-      </c>
-      <c r="G7" t="s">
-        <v>234</v>
-      </c>
-      <c r="H7" t="s">
-        <v>53</v>
-      </c>
-      <c r="I7" t="s">
-        <v>26</v>
-      </c>
-    </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>9</v>
@@ -2530,16 +2489,16 @@
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="B49" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="C49" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="D49" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="E49">
         <v>4.0999999999999996</v>
@@ -2548,7 +2507,7 @@
         <v>1924</v>
       </c>
       <c r="G49" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="I49" t="s">
         <v>14</v>
@@ -2556,13 +2515,13 @@
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="B50" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="C50" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="E50">
         <v>4.0999999999999996</v>
@@ -2571,7 +2530,7 @@
         <v>641</v>
       </c>
       <c r="G50" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="I50" t="s">
         <v>14</v>
@@ -2579,16 +2538,16 @@
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="B51" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="C51" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="D51" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="E51">
         <v>4.5999999999999996</v>
@@ -2597,7 +2556,7 @@
         <v>1073</v>
       </c>
       <c r="G51" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="I51" t="s">
         <v>14</v>
@@ -2605,16 +2564,16 @@
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="B52" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="C52" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="D52" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="E52">
         <v>3.6</v>
@@ -2623,7 +2582,7 @@
         <v>1081</v>
       </c>
       <c r="G52" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="I52" t="s">
         <v>14</v>
@@ -2631,16 +2590,16 @@
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="B53" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="C53" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="D53" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="E53">
         <v>4</v>
@@ -2649,7 +2608,7 @@
         <v>383</v>
       </c>
       <c r="G53" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="I53" t="s">
         <v>14</v>
@@ -2657,16 +2616,16 @@
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="B54" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="C54" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="D54" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="E54">
         <v>3.8</v>
@@ -2675,7 +2634,7 @@
         <v>2096</v>
       </c>
       <c r="G54" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="I54" t="s">
         <v>14</v>
@@ -2683,16 +2642,16 @@
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="B55" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="C55" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="D55" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="E55">
         <v>4</v>
@@ -2701,7 +2660,7 @@
         <v>1701</v>
       </c>
       <c r="G55" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="I55" t="s">
         <v>14</v>
@@ -2709,16 +2668,16 @@
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="B56" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C56" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="D56" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="E56">
         <v>4.2</v>
@@ -2727,7 +2686,7 @@
         <v>570</v>
       </c>
       <c r="G56" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="I56" t="s">
         <v>14</v>
@@ -2735,16 +2694,16 @@
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="B57" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="C57" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="D57" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="E57">
         <v>4.5999999999999996</v>
@@ -2753,7 +2712,7 @@
         <v>268</v>
       </c>
       <c r="G57" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="I57" t="s">
         <v>14</v>
@@ -2761,16 +2720,16 @@
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="B58" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="C58" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="D58" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="E58">
         <v>4.4000000000000004</v>
@@ -2779,7 +2738,7 @@
         <v>2466</v>
       </c>
       <c r="G58" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="I58" t="s">
         <v>14</v>
@@ -2787,16 +2746,16 @@
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="B59" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="C59" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="D59" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="E59">
         <v>4.8</v>
@@ -2805,7 +2764,7 @@
         <v>471</v>
       </c>
       <c r="G59" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="I59" t="s">
         <v>14</v>
@@ -2813,16 +2772,16 @@
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="B60" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="C60" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="D60" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="E60">
         <v>3.6</v>
@@ -2831,7 +2790,7 @@
         <v>3272</v>
       </c>
       <c r="G60" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="I60" t="s">
         <v>14</v>
@@ -2839,13 +2798,13 @@
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="B61" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="C61" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="E61">
         <v>4.2</v>
@@ -2854,7 +2813,7 @@
         <v>323</v>
       </c>
       <c r="G61" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="I61" t="s">
         <v>14</v>

--- a/restaurant_crawler/restaurant_data_台北_熱炒_20250910_192957_with_emails.xlsx
+++ b/restaurant_crawler/restaurant_data_台北_熱炒_20250910_192957_with_emails.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\slow3\OneDrive\桌面\GitHubProjects\BYOB\restaurant_crawler\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{905694E2-4437-4290-B1AC-E4E6BD55765A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0501EDC6-44F5-42F6-9F80-EAE17C326083}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="294">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="203">
   <si>
     <t>name</t>
   </si>
@@ -112,9 +112,6 @@
     <t>02 2345 3681</t>
   </si>
   <si>
-    <t>https://rink.cc/i0m5s</t>
-  </si>
-  <si>
     <t>ChIJq1i1SBKrQjQR_SF19SUBoM0</t>
   </si>
   <si>
@@ -214,48 +211,6 @@
     <t>ChIJO3kaQ2epQjQR-F1iqcYKKw4</t>
   </si>
   <si>
-    <t>仨弄砂鍋煲-台北科大|火鍋|熱炒|餐酒館|運動賽事|聚餐|寵物友善餐廳推薦|台北大安區</t>
-  </si>
-  <si>
-    <t>106台灣台北市大安區忠孝東路三段217巷3弄22號1樓</t>
-  </si>
-  <si>
-    <t>02 2775 1358</t>
-  </si>
-  <si>
-    <t>https://www.instagram.com/3long.claypot/</t>
-  </si>
-  <si>
-    <t>ChIJf1onFgCrQjQRbMXYAbT7kqM</t>
-  </si>
-  <si>
-    <t>香而廉小館</t>
-  </si>
-  <si>
-    <t>10491台灣台北市中山區合江街17巷2號</t>
-  </si>
-  <si>
-    <t>02 2501 2724</t>
-  </si>
-  <si>
-    <t>ChIJXdoi8OCrQjQRv7XFyS-_O0w</t>
-  </si>
-  <si>
-    <t>港都熱炒 中和總店Gandou restaurant(Zhonghe store)</t>
-  </si>
-  <si>
-    <t>235台灣新北市中和區大勇街12號10號</t>
-  </si>
-  <si>
-    <t>02 2940 6751</t>
-  </si>
-  <si>
-    <t>https://www.gandou.com.tw/</t>
-  </si>
-  <si>
-    <t>ChIJuZBwAAsCaDQRM2cvo8CFbe4</t>
-  </si>
-  <si>
     <t>紅翻天生猛海鮮</t>
   </si>
   <si>
@@ -304,33 +259,6 @@
     <t>salihahalin@gmail.com</t>
   </si>
   <si>
-    <t>平價快炒</t>
-  </si>
-  <si>
-    <t>106台灣台北市大安區忠孝東路四段216巷19弄10號</t>
-  </si>
-  <si>
-    <t>02 2781 1780</t>
-  </si>
-  <si>
-    <t>ChIJ8YzB5MWrQjQR0_qQu8vD7rI</t>
-  </si>
-  <si>
-    <t>大安站那邊 精緻熱炒</t>
-  </si>
-  <si>
-    <t>106台灣台北市大安區復興南路二段13-1號1樓</t>
-  </si>
-  <si>
-    <t>02 2707 8188</t>
-  </si>
-  <si>
-    <t>https://linktr.ee/DAAN.overthere_</t>
-  </si>
-  <si>
-    <t>ChIJrztn-lOrQjQRX3ZlO43HoXg</t>
-  </si>
-  <si>
     <t>臨洋港生猛活海鮮長安店</t>
   </si>
   <si>
@@ -361,30 +289,6 @@
     <t>ChIJyf0ig8mrQjQRjHYcCfHzpUE</t>
   </si>
   <si>
-    <t>筷炒KUAICHAO</t>
-  </si>
-  <si>
-    <t>11073台灣台北市信義區松仁路58號14樓</t>
-  </si>
-  <si>
-    <t>02 2758 0520</t>
-  </si>
-  <si>
-    <t>ChIJSZ89XCmrQjQRlzpduQTbttA</t>
-  </si>
-  <si>
-    <t>擱再來海鮮快炒店</t>
-  </si>
-  <si>
-    <t>100台灣台北市中正区罗斯福路三段244巷12-1號1樓</t>
-  </si>
-  <si>
-    <t>02 8369 1808</t>
-  </si>
-  <si>
-    <t>ChIJ7aTC9I6pQjQRKtS6QmUbOvI</t>
-  </si>
-  <si>
     <t>鮮定味生猛海鮮</t>
   </si>
   <si>
@@ -415,18 +319,6 @@
     <t>ChIJcaKv3sOrQjQRE8zBcA2QiNY</t>
   </si>
   <si>
-    <t>一極鮮熱炒</t>
-  </si>
-  <si>
-    <t>111台灣台北市士林區福國路95之3號</t>
-  </si>
-  <si>
-    <t>02 2833 1722</t>
-  </si>
-  <si>
-    <t>ChIJ-188RpauQjQR3gJn5Szp74s</t>
-  </si>
-  <si>
     <t>鮮定味生猛活海鮮</t>
   </si>
   <si>
@@ -442,21 +334,6 @@
     <t>ChIJRXsgpmWpQjQREaCgZsz4zwY</t>
   </si>
   <si>
-    <t>大道18號精緻熱炒</t>
-  </si>
-  <si>
-    <t>106台灣台北市大安區市民大道四段18號</t>
-  </si>
-  <si>
-    <t>02 2711 0985</t>
-  </si>
-  <si>
-    <t>https://www.facebook.com/groups/983589249549831</t>
-  </si>
-  <si>
-    <t>ChIJvyiRElCrQjQRRIy23aBJwbQ</t>
-  </si>
-  <si>
     <t>良友小館</t>
   </si>
   <si>
@@ -472,18 +349,6 @@
     <t>ChIJ7e_rfHmpQjQRoQFSKIVubuc</t>
   </si>
   <si>
-    <t>欣海岸海鮮料理</t>
-  </si>
-  <si>
-    <t>105台灣台北市松山區八德路三段158巷1-2號</t>
-  </si>
-  <si>
-    <t>0919 191 820</t>
-  </si>
-  <si>
-    <t>ChIJWVfyM4irQjQRhBwgmaLujLs</t>
-  </si>
-  <si>
     <t>豪香熱炒</t>
   </si>
   <si>
@@ -499,30 +364,9 @@
     <t>ChIJ0UNv3YupQjQRxu2l8vvS3zo</t>
   </si>
   <si>
-    <t>熱炒店</t>
-  </si>
-  <si>
-    <t>103台灣台北市大同區南京西路262巷11號</t>
-  </si>
-  <si>
-    <t>0928 118 482</t>
-  </si>
-  <si>
-    <t>ChIJNfiQ0mGpQjQRo5qOceI9kE0</t>
-  </si>
-  <si>
-    <t>八仙炭烤熱炒</t>
-  </si>
-  <si>
     <t>106台灣台北市大安區新生南路二段28號</t>
   </si>
   <si>
-    <t>02 2321 4507</t>
-  </si>
-  <si>
-    <t>ChIJjStauYGpQjQR6Cqqnlq3bi4</t>
-  </si>
-  <si>
     <t>夯店-懷舊食堂（燒烤 熱炒 海鮮 鍋物）</t>
   </si>
   <si>
@@ -538,18 +382,6 @@
     <t>ChIJrwQO5QcCaDQRKMc_MVmqMVg</t>
   </si>
   <si>
-    <t>尚介青鵝肉城熱炒</t>
-  </si>
-  <si>
-    <t>100台灣台北市中正區中華路二段311巷14號</t>
-  </si>
-  <si>
-    <t>02 2301 2244</t>
-  </si>
-  <si>
-    <t>ChIJK0aHJLupQjQRBynJ1eND3xk</t>
-  </si>
-  <si>
     <t>鱘鱻小館</t>
   </si>
   <si>
@@ -577,18 +409,6 @@
     <t>ChIJre9cvoGpQjQRA3mn9UiYa0A</t>
   </si>
   <si>
-    <t>好菜場生猛海鮮</t>
-  </si>
-  <si>
-    <t>116台灣台北市文山區興隆路一段225號</t>
-  </si>
-  <si>
-    <t>02 8931 7131</t>
-  </si>
-  <si>
-    <t>ChIJN5bBRRuqQjQRE-b7hbgkJNQ</t>
-  </si>
-  <si>
     <t>海味豐海產店</t>
   </si>
   <si>
@@ -637,45 +457,6 @@
     <t>chien2005168@gmail.com</t>
   </si>
   <si>
-    <t>有有1969</t>
-  </si>
-  <si>
-    <t>104台灣台北市中山區遼寧街48號</t>
-  </si>
-  <si>
-    <t>02 2776 0443</t>
-  </si>
-  <si>
-    <t>http://有有1969.com/?utm_source=gmb&amp;utm_medium=referral</t>
-  </si>
-  <si>
-    <t>ChIJUVfSk46rQjQRjSYEdTmKW8Q</t>
-  </si>
-  <si>
-    <t>熱翻天生猛海鮮</t>
-  </si>
-  <si>
-    <t>10665台灣台北市大安區復興南路二段154號</t>
-  </si>
-  <si>
-    <t>02 2784 9877</t>
-  </si>
-  <si>
-    <t>ChIJI4hkcCyqQjQR_jvfIa2QoPs</t>
-  </si>
-  <si>
-    <t>駱記小炒</t>
-  </si>
-  <si>
-    <t>106台灣台北市大安區通化街39巷50弄27號</t>
-  </si>
-  <si>
-    <t>02 2708 1027</t>
-  </si>
-  <si>
-    <t>ChIJeRfjbMurQjQRKTmzUGfnWIU</t>
-  </si>
-  <si>
     <t>噗嚨哄海鮮餐廳</t>
   </si>
   <si>
@@ -691,30 +472,6 @@
     <t>ChIJpf2GDsmrQjQR0i7un1n9S7w</t>
   </si>
   <si>
-    <t>小漁村精緻海鮮平價快炒</t>
-  </si>
-  <si>
-    <t>100台灣台北市中正區中華路二段311巷19號</t>
-  </si>
-  <si>
-    <t>02 2303 6976</t>
-  </si>
-  <si>
-    <t>ChIJ83F0JbupQjQRHfl00WP-Nh0</t>
-  </si>
-  <si>
-    <t>菜真香</t>
-  </si>
-  <si>
-    <t>106台灣台北市大安區安和路二段59巷12號</t>
-  </si>
-  <si>
-    <t>02 2325 3658</t>
-  </si>
-  <si>
-    <t>ChIJc0bak8yrQjQRa6SGK9i5gks</t>
-  </si>
-  <si>
     <t>半斤九兩食品有限公司-台北 台菜海鮮熱炒 喜宴 謝師宴 同學會聚餐 尾牙 活海鮮 辦桌 推薦中餐廳 生猛海鮮餐廳推薦 年菜圍爐 外帶年菜 年夜飯 海鮮料理 私房料理 台灣料理</t>
   </si>
   <si>
@@ -724,24 +481,9 @@
     <t>02 2541 7333</t>
   </si>
   <si>
-    <t>https://extra9.com.tw/</t>
-  </si>
-  <si>
     <t>ChIJafrv9F2pQjQRnMFSf-7Fiv8</t>
   </si>
   <si>
-    <t>十三香海鮮熱炒店</t>
-  </si>
-  <si>
-    <t>106台灣台北市大安區信義路四段345號</t>
-  </si>
-  <si>
-    <t>02 2709 5252</t>
-  </si>
-  <si>
-    <t>ChIJX-DB1curQjQRY4ErcHDn0t4</t>
-  </si>
-  <si>
     <t>船鼎海鮮創作料理</t>
   </si>
   <si>
@@ -841,27 +583,9 @@
     <t>02 3765 1103</t>
   </si>
   <si>
-    <t>https://xiaoyuanzi-rechao.weebly.com/</t>
-  </si>
-  <si>
     <t>ChIJB8HhqYurQjQRSOLmsl5TQFQ</t>
   </si>
   <si>
-    <t>海九澎湖海鮮餐廳</t>
-  </si>
-  <si>
-    <t>104台灣台北市中山區長安東路二段170號</t>
-  </si>
-  <si>
-    <t>02 2751 7272</t>
-  </si>
-  <si>
-    <t>http://www.hijo.com.tw/</t>
-  </si>
-  <si>
-    <t>ChIJC8Sm1d6rQjQRkybRsVasbvo</t>
-  </si>
-  <si>
     <t>皇茗薑母鴨（串燒、熱炒）【台北 大同區 人氣串燒、熱炒、薑母鴨推薦 】必吃薑母鴨|聚餐餐廳|必吃美食|熱門薑母鴨|在地推薦火鍋|好吃串燒|平價熱炒消夜推薦 延三夜市 大橋頭 附近美食2025 網友推薦首選 PTT Dcard</t>
   </si>
   <si>
@@ -892,16 +616,19 @@
     <t>ChIJLycvqGWpQjQRYcZmq3ooQvI</t>
   </si>
   <si>
-    <t>天天來海鮮熱炒</t>
-  </si>
-  <si>
-    <t>108台灣台北市萬華區萬大路11號</t>
-  </si>
-  <si>
-    <t>0931 153 207</t>
-  </si>
-  <si>
-    <t>ChIJLVL6UqmpQjQRsAKbCx_vhmM</t>
+    <t>https://www.facebook.com/profile.php?id=100092552531378</t>
+  </si>
+  <si>
+    <t>smallkaykay@yahoo.com.tw</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/profile.php?id=100054314000038#</t>
+  </si>
+  <si>
+    <t>smallyard2308@gmail.com</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/profile.php?id=100093013008736</t>
   </si>
 </sst>
 </file>
@@ -1280,7 +1007,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I61"/>
+  <dimension ref="A1:K40"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="27.125" customWidth="1"/>
@@ -1349,16 +1076,16 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" t="s">
         <v>32</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>33</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" s="2" t="s">
         <v>34</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>35</v>
       </c>
       <c r="E3">
         <v>4.4000000000000004</v>
@@ -1367,10 +1094,10 @@
         <v>1132</v>
       </c>
       <c r="G3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H3" t="s">
         <v>36</v>
-      </c>
-      <c r="H3" t="s">
-        <v>37</v>
       </c>
       <c r="I3" t="s">
         <v>26</v>
@@ -1378,16 +1105,16 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B4" t="s">
         <v>48</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>49</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" s="2" t="s">
         <v>50</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>51</v>
       </c>
       <c r="E4">
         <v>4.0999999999999996</v>
@@ -1396,10 +1123,10 @@
         <v>2232</v>
       </c>
       <c r="G4" t="s">
+        <v>51</v>
+      </c>
+      <c r="H4" t="s">
         <v>52</v>
-      </c>
-      <c r="H4" t="s">
-        <v>53</v>
       </c>
       <c r="I4" t="s">
         <v>26</v>
@@ -1407,16 +1134,16 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>88</v>
+        <v>73</v>
       </c>
       <c r="B5" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="C5" t="s">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="E5">
         <v>3.9</v>
@@ -1425,10 +1152,10 @@
         <v>2310</v>
       </c>
       <c r="G5" t="s">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="H5" t="s">
-        <v>93</v>
+        <v>78</v>
       </c>
       <c r="I5" t="s">
         <v>26</v>
@@ -1436,16 +1163,16 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>199</v>
+        <v>139</v>
       </c>
       <c r="B6" t="s">
-        <v>200</v>
+        <v>140</v>
       </c>
       <c r="C6" t="s">
-        <v>201</v>
+        <v>141</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>202</v>
+        <v>142</v>
       </c>
       <c r="E6">
         <v>4.0999999999999996</v>
@@ -1454,88 +1181,65 @@
         <v>275</v>
       </c>
       <c r="G6" t="s">
-        <v>203</v>
+        <v>143</v>
       </c>
       <c r="H6" t="s">
-        <v>204</v>
+        <v>144</v>
       </c>
       <c r="I6" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" t="s">
-        <v>11</v>
-      </c>
-      <c r="D8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E8">
-        <v>4.7</v>
-      </c>
-      <c r="F8">
-        <v>2911</v>
-      </c>
-      <c r="G8" t="s">
-        <v>13</v>
-      </c>
-      <c r="I8" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9" t="s">
-        <v>17</v>
-      </c>
-      <c r="D9" t="s">
-        <v>18</v>
-      </c>
-      <c r="E9">
-        <v>4.9000000000000004</v>
-      </c>
-      <c r="F9">
-        <v>15322</v>
-      </c>
-      <c r="G9" t="s">
-        <v>19</v>
-      </c>
-      <c r="I9" t="s">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E7">
+        <v>4.5</v>
+      </c>
+      <c r="F7">
+        <v>1748</v>
+      </c>
+      <c r="G7" t="s">
+        <v>41</v>
+      </c>
+      <c r="H7" t="s">
+        <v>199</v>
+      </c>
+      <c r="I7" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="C10" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="D10" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="E10">
-        <v>4.9000000000000004</v>
+        <v>4.7</v>
       </c>
       <c r="F10">
-        <v>3165</v>
+        <v>2911</v>
       </c>
       <c r="G10" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="I10" t="s">
         <v>14</v>
@@ -1543,25 +1247,25 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="B11" t="s">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="C11" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="D11" t="s">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="E11">
-        <v>4.5</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="F11">
-        <v>1748</v>
+        <v>15322</v>
       </c>
       <c r="G11" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="I11" t="s">
         <v>14</v>
@@ -1569,25 +1273,25 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="B12" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="C12" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="D12" t="s">
-        <v>46</v>
+        <v>198</v>
       </c>
       <c r="E12">
-        <v>4.4000000000000004</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="F12">
-        <v>1237</v>
+        <v>3165</v>
       </c>
       <c r="G12" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="I12" t="s">
         <v>14</v>
@@ -1595,25 +1299,25 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="B13" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="C13" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="D13" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="E13">
-        <v>4.2</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="F13">
-        <v>2112</v>
+        <v>1237</v>
       </c>
       <c r="G13" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="I13" t="s">
         <v>14</v>
@@ -1621,25 +1325,25 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="B14" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="C14" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D14" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="E14">
-        <v>4.5999999999999996</v>
+        <v>4.2</v>
       </c>
       <c r="F14">
-        <v>2744</v>
+        <v>2112</v>
       </c>
       <c r="G14" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="I14" t="s">
         <v>14</v>
@@ -1647,25 +1351,25 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="B15" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="C15" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="D15" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="E15">
-        <v>4.9000000000000004</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="F15">
-        <v>903</v>
+        <v>2744</v>
       </c>
       <c r="G15" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="I15" t="s">
         <v>14</v>
@@ -1673,423 +1377,444 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
+        <v>63</v>
+      </c>
+      <c r="B16" t="s">
+        <v>64</v>
+      </c>
+      <c r="C16" t="s">
+        <v>65</v>
+      </c>
+      <c r="D16" t="s">
+        <v>66</v>
+      </c>
+      <c r="E16">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="F16">
+        <v>4369</v>
+      </c>
+      <c r="G16" t="s">
+        <v>67</v>
+      </c>
+      <c r="I16" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>68</v>
+      </c>
+      <c r="B17" t="s">
         <v>69</v>
       </c>
-      <c r="B16" t="s">
+      <c r="C17" t="s">
         <v>70</v>
       </c>
-      <c r="C16" t="s">
+      <c r="D17" t="s">
         <v>71</v>
       </c>
-      <c r="E16">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="F16">
-        <v>1648</v>
-      </c>
-      <c r="G16" t="s">
+      <c r="E17">
+        <v>4.5</v>
+      </c>
+      <c r="F17">
+        <v>263</v>
+      </c>
+      <c r="G17" t="s">
         <v>72</v>
       </c>
-      <c r="I16" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>73</v>
-      </c>
-      <c r="B17" t="s">
-        <v>74</v>
-      </c>
-      <c r="C17" t="s">
-        <v>75</v>
-      </c>
-      <c r="D17" t="s">
-        <v>76</v>
-      </c>
-      <c r="E17">
-        <v>4.3</v>
-      </c>
-      <c r="F17">
-        <v>1949</v>
-      </c>
-      <c r="G17" t="s">
-        <v>77</v>
-      </c>
       <c r="I17" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C18" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D18" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E18">
         <v>4.0999999999999996</v>
       </c>
       <c r="F18">
-        <v>4369</v>
+        <v>4096</v>
       </c>
       <c r="G18" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I18" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B19" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D19" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E19">
-        <v>4.5</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="F19">
-        <v>263</v>
+        <v>2562</v>
       </c>
       <c r="G19" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I19" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="B20" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="C20" t="s">
-        <v>96</v>
+        <v>91</v>
+      </c>
+      <c r="D20" t="s">
+        <v>92</v>
       </c>
       <c r="E20">
         <v>4.0999999999999996</v>
       </c>
       <c r="F20">
-        <v>1770</v>
+        <v>1922</v>
       </c>
       <c r="G20" t="s">
+        <v>93</v>
+      </c>
+      <c r="I20" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>94</v>
+      </c>
+      <c r="B21" t="s">
+        <v>95</v>
+      </c>
+      <c r="C21" t="s">
+        <v>96</v>
+      </c>
+      <c r="D21" t="s">
         <v>97</v>
       </c>
-      <c r="I20" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
+      <c r="E21">
+        <v>4</v>
+      </c>
+      <c r="F21">
+        <v>2248</v>
+      </c>
+      <c r="G21" t="s">
         <v>98</v>
       </c>
-      <c r="B21" t="s">
+      <c r="I21" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
         <v>99</v>
       </c>
-      <c r="C21" t="s">
+      <c r="B22" t="s">
         <v>100</v>
       </c>
-      <c r="D21" t="s">
+      <c r="C22" t="s">
         <v>101</v>
       </c>
-      <c r="E21">
-        <v>4.2</v>
-      </c>
-      <c r="F21">
-        <v>722</v>
-      </c>
-      <c r="G21" t="s">
+      <c r="D22" t="s">
         <v>102</v>
       </c>
-      <c r="I21" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
+      <c r="E22">
+        <v>4</v>
+      </c>
+      <c r="F22">
+        <v>3472</v>
+      </c>
+      <c r="G22" t="s">
         <v>103</v>
       </c>
-      <c r="B22" t="s">
+      <c r="I22" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
         <v>104</v>
       </c>
-      <c r="C22" t="s">
+      <c r="B23" t="s">
         <v>105</v>
       </c>
-      <c r="D22" t="s">
+      <c r="C23" t="s">
         <v>106</v>
       </c>
-      <c r="E22">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="F22">
-        <v>4096</v>
-      </c>
-      <c r="G22" t="s">
+      <c r="D23" t="s">
         <v>107</v>
       </c>
-      <c r="I22" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
+      <c r="E23">
+        <v>4.3</v>
+      </c>
+      <c r="F23">
+        <v>2208</v>
+      </c>
+      <c r="G23" t="s">
         <v>108</v>
       </c>
-      <c r="B23" t="s">
+      <c r="I23" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
         <v>109</v>
       </c>
-      <c r="C23" t="s">
+      <c r="B24" t="s">
         <v>110</v>
       </c>
-      <c r="D23" t="s">
+      <c r="C24" t="s">
         <v>111</v>
       </c>
-      <c r="E23">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="F23">
-        <v>2562</v>
-      </c>
-      <c r="G23" t="s">
+      <c r="D24" t="s">
         <v>112</v>
       </c>
-      <c r="I23" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
+      <c r="E24">
+        <v>3.8</v>
+      </c>
+      <c r="F24">
+        <v>915</v>
+      </c>
+      <c r="G24" t="s">
         <v>113</v>
       </c>
-      <c r="B24" t="s">
-        <v>114</v>
-      </c>
-      <c r="C24" t="s">
+      <c r="I24" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
         <v>115</v>
       </c>
-      <c r="E24">
-        <v>4.3</v>
-      </c>
-      <c r="F24">
-        <v>1090</v>
-      </c>
-      <c r="G24" t="s">
+      <c r="B25" t="s">
         <v>116</v>
       </c>
-      <c r="I24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
+      <c r="C25" t="s">
         <v>117</v>
       </c>
-      <c r="B25" t="s">
+      <c r="D25" t="s">
         <v>118</v>
       </c>
-      <c r="C25" t="s">
+      <c r="E25">
+        <v>4.5</v>
+      </c>
+      <c r="F25">
+        <v>167</v>
+      </c>
+      <c r="G25" t="s">
         <v>119</v>
       </c>
-      <c r="E25">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="F25">
-        <v>419</v>
-      </c>
-      <c r="G25" t="s">
+      <c r="I25" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
         <v>120</v>
       </c>
-      <c r="I25" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
+      <c r="B26" t="s">
         <v>121</v>
       </c>
-      <c r="B26" t="s">
+      <c r="C26" t="s">
         <v>122</v>
       </c>
-      <c r="C26" t="s">
+      <c r="D26" t="s">
         <v>123</v>
-      </c>
-      <c r="D26" t="s">
-        <v>124</v>
       </c>
       <c r="E26">
         <v>4.0999999999999996</v>
       </c>
       <c r="F26">
-        <v>1922</v>
+        <v>883</v>
       </c>
       <c r="G26" t="s">
+        <v>124</v>
+      </c>
+      <c r="I26" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
         <v>125</v>
       </c>
-      <c r="I26" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
+      <c r="B27" t="s">
+        <v>114</v>
+      </c>
+      <c r="C27" t="s">
         <v>126</v>
       </c>
-      <c r="B27" t="s">
+      <c r="D27" t="s">
         <v>127</v>
       </c>
-      <c r="C27" t="s">
+      <c r="E27">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="F27">
+        <v>1272</v>
+      </c>
+      <c r="G27" t="s">
         <v>128</v>
       </c>
-      <c r="D27" t="s">
+      <c r="I27" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
         <v>129</v>
       </c>
-      <c r="E27">
-        <v>4</v>
-      </c>
-      <c r="F27">
-        <v>2248</v>
-      </c>
-      <c r="G27" t="s">
+      <c r="B28" t="s">
         <v>130</v>
       </c>
-      <c r="I27" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
+      <c r="C28" t="s">
         <v>131</v>
       </c>
-      <c r="B28" t="s">
+      <c r="D28" t="s">
         <v>132</v>
       </c>
-      <c r="C28" t="s">
+      <c r="E28">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="F28">
+        <v>1250</v>
+      </c>
+      <c r="G28" t="s">
         <v>133</v>
       </c>
-      <c r="E28">
-        <v>4</v>
-      </c>
-      <c r="F28">
-        <v>2203</v>
-      </c>
-      <c r="G28" t="s">
+      <c r="I28" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
         <v>134</v>
       </c>
-      <c r="I28" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
+      <c r="B29" t="s">
         <v>135</v>
       </c>
-      <c r="B29" t="s">
+      <c r="C29" t="s">
         <v>136</v>
       </c>
-      <c r="C29" t="s">
+      <c r="D29" t="s">
         <v>137</v>
-      </c>
-      <c r="D29" t="s">
-        <v>138</v>
       </c>
       <c r="E29">
         <v>4</v>
       </c>
       <c r="F29">
-        <v>3472</v>
+        <v>1516</v>
       </c>
       <c r="G29" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I29" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="B30" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="C30" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="D30" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="E30">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="F30">
-        <v>1304</v>
+        <v>1645</v>
       </c>
       <c r="G30" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="I30" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="B31" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="C31" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="D31" t="s">
-        <v>148</v>
+        <v>200</v>
       </c>
       <c r="E31">
-        <v>4.3</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="F31">
-        <v>2208</v>
+        <v>1924</v>
       </c>
       <c r="G31" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="I31" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="K31">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="B32" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="C32" t="s">
-        <v>152</v>
+        <v>156</v>
+      </c>
+      <c r="D32" t="s">
+        <v>157</v>
       </c>
       <c r="E32">
-        <v>4.4000000000000004</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="F32">
-        <v>1301</v>
+        <v>1073</v>
       </c>
       <c r="G32" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="I32" t="s">
         <v>14</v>
@@ -2097,25 +1822,25 @@
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="B33" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="C33" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="D33" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="E33">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="F33">
-        <v>915</v>
+        <v>1081</v>
       </c>
       <c r="G33" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="I33" t="s">
         <v>14</v>
@@ -2123,22 +1848,25 @@
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="B34" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="C34" t="s">
-        <v>161</v>
+        <v>166</v>
+      </c>
+      <c r="D34" t="s">
+        <v>167</v>
       </c>
       <c r="E34">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="F34">
-        <v>53</v>
+        <v>383</v>
       </c>
       <c r="G34" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="I34" t="s">
         <v>14</v>
@@ -2146,22 +1874,25 @@
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="B35" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="C35" t="s">
-        <v>165</v>
+        <v>171</v>
+      </c>
+      <c r="D35" t="s">
+        <v>172</v>
       </c>
       <c r="E35">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="F35">
-        <v>1178</v>
+        <v>2096</v>
       </c>
       <c r="G35" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="I35" t="s">
         <v>14</v>
@@ -2169,25 +1900,25 @@
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="B36" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="C36" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="D36" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="E36">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="F36">
-        <v>167</v>
+        <v>1701</v>
       </c>
       <c r="G36" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="I36" t="s">
         <v>14</v>
@@ -2195,22 +1926,25 @@
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="B37" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="C37" t="s">
-        <v>174</v>
+        <v>181</v>
+      </c>
+      <c r="D37" t="s">
+        <v>182</v>
       </c>
       <c r="E37">
-        <v>4.0999999999999996</v>
+        <v>4.2</v>
       </c>
       <c r="F37">
-        <v>792</v>
+        <v>570</v>
       </c>
       <c r="G37" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="I37" t="s">
         <v>14</v>
@@ -2218,25 +1952,28 @@
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="B38" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="C38" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="D38" t="s">
-        <v>179</v>
+        <v>202</v>
       </c>
       <c r="E38">
-        <v>4.0999999999999996</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="F38">
-        <v>883</v>
+        <v>268</v>
       </c>
       <c r="G38" t="s">
-        <v>180</v>
+        <v>187</v>
+      </c>
+      <c r="H38" t="s">
+        <v>201</v>
       </c>
       <c r="I38" t="s">
         <v>14</v>
@@ -2244,25 +1981,25 @@
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="B39" t="s">
-        <v>164</v>
+        <v>189</v>
       </c>
       <c r="C39" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="D39" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="E39">
-        <v>4.0999999999999996</v>
+        <v>4.8</v>
       </c>
       <c r="F39">
-        <v>1272</v>
+        <v>471</v>
       </c>
       <c r="G39" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="I39" t="s">
         <v>14</v>
@@ -2270,558 +2007,33 @@
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="B40" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="C40" t="s">
-        <v>187</v>
+        <v>195</v>
+      </c>
+      <c r="D40" t="s">
+        <v>196</v>
       </c>
       <c r="E40">
-        <v>4.0999999999999996</v>
+        <v>3.6</v>
       </c>
       <c r="F40">
-        <v>640</v>
+        <v>3272</v>
       </c>
       <c r="G40" t="s">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="I40" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
-        <v>189</v>
-      </c>
-      <c r="B41" t="s">
-        <v>190</v>
-      </c>
-      <c r="C41" t="s">
-        <v>191</v>
-      </c>
-      <c r="D41" t="s">
-        <v>192</v>
-      </c>
-      <c r="E41">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="F41">
-        <v>1250</v>
-      </c>
-      <c r="G41" t="s">
-        <v>193</v>
-      </c>
-      <c r="I41" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
-        <v>194</v>
-      </c>
-      <c r="B42" t="s">
-        <v>195</v>
-      </c>
-      <c r="C42" t="s">
-        <v>196</v>
-      </c>
-      <c r="D42" t="s">
-        <v>197</v>
-      </c>
-      <c r="E42">
-        <v>4</v>
-      </c>
-      <c r="F42">
-        <v>1516</v>
-      </c>
-      <c r="G42" t="s">
-        <v>198</v>
-      </c>
-      <c r="I42" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
-        <v>205</v>
-      </c>
-      <c r="B43" t="s">
-        <v>206</v>
-      </c>
-      <c r="C43" t="s">
-        <v>207</v>
-      </c>
-      <c r="D43" t="s">
-        <v>208</v>
-      </c>
-      <c r="E43">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="F43">
-        <v>1245</v>
-      </c>
-      <c r="G43" t="s">
-        <v>209</v>
-      </c>
-      <c r="I43" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
-        <v>210</v>
-      </c>
-      <c r="B44" t="s">
-        <v>211</v>
-      </c>
-      <c r="C44" t="s">
-        <v>212</v>
-      </c>
-      <c r="E44">
-        <v>3.8</v>
-      </c>
-      <c r="F44">
-        <v>1003</v>
-      </c>
-      <c r="G44" t="s">
-        <v>213</v>
-      </c>
-      <c r="I44" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
-        <v>214</v>
-      </c>
-      <c r="B45" t="s">
-        <v>215</v>
-      </c>
-      <c r="C45" t="s">
-        <v>216</v>
-      </c>
-      <c r="E45">
-        <v>2.9</v>
-      </c>
-      <c r="F45">
-        <v>1783</v>
-      </c>
-      <c r="G45" t="s">
-        <v>217</v>
-      </c>
-      <c r="I45" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
-        <v>218</v>
-      </c>
-      <c r="B46" t="s">
-        <v>219</v>
-      </c>
-      <c r="C46" t="s">
-        <v>220</v>
-      </c>
-      <c r="D46" t="s">
-        <v>221</v>
-      </c>
-      <c r="E46">
-        <v>4.5</v>
-      </c>
-      <c r="F46">
-        <v>1645</v>
-      </c>
-      <c r="G46" t="s">
-        <v>222</v>
-      </c>
-      <c r="I46" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
-        <v>223</v>
-      </c>
-      <c r="B47" t="s">
-        <v>224</v>
-      </c>
-      <c r="C47" t="s">
-        <v>225</v>
-      </c>
-      <c r="E47">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="F47">
-        <v>631</v>
-      </c>
-      <c r="G47" t="s">
-        <v>226</v>
-      </c>
-      <c r="I47" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A48" t="s">
-        <v>227</v>
-      </c>
-      <c r="B48" t="s">
-        <v>228</v>
-      </c>
-      <c r="C48" t="s">
-        <v>229</v>
-      </c>
-      <c r="E48">
-        <v>4.2</v>
-      </c>
-      <c r="F48">
-        <v>411</v>
-      </c>
-      <c r="G48" t="s">
-        <v>230</v>
-      </c>
-      <c r="I48" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A49" t="s">
-        <v>231</v>
-      </c>
-      <c r="B49" t="s">
-        <v>232</v>
-      </c>
-      <c r="C49" t="s">
-        <v>233</v>
-      </c>
-      <c r="D49" t="s">
-        <v>234</v>
-      </c>
-      <c r="E49">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="F49">
-        <v>1924</v>
-      </c>
-      <c r="G49" t="s">
-        <v>235</v>
-      </c>
-      <c r="I49" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
-        <v>236</v>
-      </c>
-      <c r="B50" t="s">
-        <v>237</v>
-      </c>
-      <c r="C50" t="s">
-        <v>238</v>
-      </c>
-      <c r="E50">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="F50">
-        <v>641</v>
-      </c>
-      <c r="G50" t="s">
-        <v>239</v>
-      </c>
-      <c r="I50" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A51" t="s">
-        <v>240</v>
-      </c>
-      <c r="B51" t="s">
-        <v>241</v>
-      </c>
-      <c r="C51" t="s">
-        <v>242</v>
-      </c>
-      <c r="D51" t="s">
-        <v>243</v>
-      </c>
-      <c r="E51">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="F51">
-        <v>1073</v>
-      </c>
-      <c r="G51" t="s">
-        <v>244</v>
-      </c>
-      <c r="I51" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A52" t="s">
-        <v>245</v>
-      </c>
-      <c r="B52" t="s">
-        <v>246</v>
-      </c>
-      <c r="C52" t="s">
-        <v>247</v>
-      </c>
-      <c r="D52" t="s">
-        <v>248</v>
-      </c>
-      <c r="E52">
-        <v>3.6</v>
-      </c>
-      <c r="F52">
-        <v>1081</v>
-      </c>
-      <c r="G52" t="s">
-        <v>249</v>
-      </c>
-      <c r="I52" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A53" t="s">
-        <v>250</v>
-      </c>
-      <c r="B53" t="s">
-        <v>251</v>
-      </c>
-      <c r="C53" t="s">
-        <v>252</v>
-      </c>
-      <c r="D53" t="s">
-        <v>253</v>
-      </c>
-      <c r="E53">
-        <v>4</v>
-      </c>
-      <c r="F53">
-        <v>383</v>
-      </c>
-      <c r="G53" t="s">
-        <v>254</v>
-      </c>
-      <c r="I53" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A54" t="s">
-        <v>255</v>
-      </c>
-      <c r="B54" t="s">
-        <v>256</v>
-      </c>
-      <c r="C54" t="s">
-        <v>257</v>
-      </c>
-      <c r="D54" t="s">
-        <v>258</v>
-      </c>
-      <c r="E54">
-        <v>3.8</v>
-      </c>
-      <c r="F54">
-        <v>2096</v>
-      </c>
-      <c r="G54" t="s">
-        <v>259</v>
-      </c>
-      <c r="I54" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A55" t="s">
-        <v>260</v>
-      </c>
-      <c r="B55" t="s">
-        <v>261</v>
-      </c>
-      <c r="C55" t="s">
-        <v>262</v>
-      </c>
-      <c r="D55" t="s">
-        <v>263</v>
-      </c>
-      <c r="E55">
-        <v>4</v>
-      </c>
-      <c r="F55">
-        <v>1701</v>
-      </c>
-      <c r="G55" t="s">
-        <v>264</v>
-      </c>
-      <c r="I55" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A56" t="s">
-        <v>265</v>
-      </c>
-      <c r="B56" t="s">
-        <v>266</v>
-      </c>
-      <c r="C56" t="s">
-        <v>267</v>
-      </c>
-      <c r="D56" t="s">
-        <v>268</v>
-      </c>
-      <c r="E56">
-        <v>4.2</v>
-      </c>
-      <c r="F56">
-        <v>570</v>
-      </c>
-      <c r="G56" t="s">
-        <v>269</v>
-      </c>
-      <c r="I56" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A57" t="s">
-        <v>270</v>
-      </c>
-      <c r="B57" t="s">
-        <v>271</v>
-      </c>
-      <c r="C57" t="s">
-        <v>272</v>
-      </c>
-      <c r="D57" t="s">
-        <v>273</v>
-      </c>
-      <c r="E57">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="F57">
-        <v>268</v>
-      </c>
-      <c r="G57" t="s">
-        <v>274</v>
-      </c>
-      <c r="I57" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A58" t="s">
-        <v>275</v>
-      </c>
-      <c r="B58" t="s">
-        <v>276</v>
-      </c>
-      <c r="C58" t="s">
-        <v>277</v>
-      </c>
-      <c r="D58" t="s">
-        <v>278</v>
-      </c>
-      <c r="E58">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="F58">
-        <v>2466</v>
-      </c>
-      <c r="G58" t="s">
-        <v>279</v>
-      </c>
-      <c r="I58" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A59" t="s">
-        <v>280</v>
-      </c>
-      <c r="B59" t="s">
-        <v>281</v>
-      </c>
-      <c r="C59" t="s">
-        <v>282</v>
-      </c>
-      <c r="D59" t="s">
-        <v>283</v>
-      </c>
-      <c r="E59">
-        <v>4.8</v>
-      </c>
-      <c r="F59">
-        <v>471</v>
-      </c>
-      <c r="G59" t="s">
-        <v>284</v>
-      </c>
-      <c r="I59" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A60" t="s">
-        <v>285</v>
-      </c>
-      <c r="B60" t="s">
-        <v>286</v>
-      </c>
-      <c r="C60" t="s">
-        <v>287</v>
-      </c>
-      <c r="D60" t="s">
-        <v>288</v>
-      </c>
-      <c r="E60">
-        <v>3.6</v>
-      </c>
-      <c r="F60">
-        <v>3272</v>
-      </c>
-      <c r="G60" t="s">
-        <v>289</v>
-      </c>
-      <c r="I60" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A61" t="s">
-        <v>290</v>
-      </c>
-      <c r="B61" t="s">
-        <v>291</v>
-      </c>
-      <c r="C61" t="s">
-        <v>292</v>
-      </c>
-      <c r="E61">
-        <v>4.2</v>
-      </c>
-      <c r="F61">
-        <v>323</v>
-      </c>
-      <c r="G61" t="s">
-        <v>293</v>
-      </c>
-      <c r="I61" t="s">
-        <v>14</v>
-      </c>
-    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I61">
-    <sortCondition ref="I2:I61"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I40">
+    <sortCondition ref="I2:I40"/>
   </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
